--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486915_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486915_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.422599999999999</v>
+        <v>6.2247</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9608</v>
+        <v>2.8301</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4618</v>
+        <v>3.3947</v>
       </c>
       <c r="G2" t="n">
         <v>3.3331</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9028</v>
+        <v>1.7048</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9403</v>
+        <v>0.8095</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9625</v>
+        <v>0.8954</v>
       </c>
       <c r="V2" t="n">
         <v>2.0082</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9752</v>
+        <v>5.7223</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0789</v>
+        <v>4.7476</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8962</v>
+        <v>0.9748</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6274</v>
+        <v>4.8602</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6167</v>
+        <v>1.9397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0107</v>
+        <v>2.9205</v>
       </c>
       <c r="J3" t="n">
-        <v>0.498</v>
+        <v>4.612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.419</v>
+        <v>1.5996</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0789</v>
+        <v>3.0124</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1294</v>
+        <v>0.2482</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1977</v>
+        <v>0.3401</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0682</v>
+        <v>-0.092</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="Q3" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.09470000000000001</v>
+      </c>
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.4374</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.3827</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.5728</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.1901</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.5277</v>
-      </c>
       <c r="W3" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9556</v>
+        <v>4.1959</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1587</v>
+        <v>3.0329</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7969000000000001</v>
+        <v>1.163</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8602</v>
+        <v>0.6274</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9397</v>
+        <v>0.6167</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9205</v>
+        <v>0.0107</v>
       </c>
       <c r="J4" t="n">
-        <v>4.612</v>
+        <v>0.498</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5996</v>
+        <v>0.419</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0124</v>
+        <v>0.0789</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2482</v>
+        <v>0.1294</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3401</v>
+        <v>0.1977</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.092</v>
+        <v>-0.0682</v>
       </c>
       <c r="P4" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5206</v>
+        <v>0.6034</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.248</v>
+        <v>0.5268</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2726</v>
+        <v>0.0766</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5277</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.0082</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6578</v>
+        <v>2.3479</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1108</v>
+        <v>3.3859</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.453</v>
+        <v>-1.038</v>
       </c>
       <c r="G5" t="n">
         <v>3.0592</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7423</v>
+        <v>-0.0523</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3489</v>
+        <v>-0.0738</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3935</v>
+        <v>0.0215</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0698</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8208</v>
+        <v>1.842</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8114</v>
+        <v>-0.9087</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6322</v>
+        <v>2.7508</v>
       </c>
       <c r="G6" t="n">
         <v>1.3805</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3625</v>
+        <v>0.6587</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8486</v>
+        <v>0.0541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4861</v>
+        <v>0.6046</v>
       </c>
       <c r="V6" t="n">
         <v>0.8295</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2442</v>
+        <v>-0.7212</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7809</v>
+        <v>-1.2579</v>
       </c>
       <c r="F7" t="n">
         <v>0.5368000000000001</v>
@@ -1000,10 +1000,10 @@
         <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.3797</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7246</v>
+        <v>-0.2016</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1781</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3878</v>
+        <v>-0.9784</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6084</v>
+        <v>-2.2287</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2206</v>
+        <v>1.2503</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4238</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1592</v>
+        <v>0.5686</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1513</v>
+        <v>0.2284</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3105</v>
+        <v>0.3401</v>
       </c>
       <c r="V8" t="n">
         <v>0.1088</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6002</v>
+        <v>-2.1076</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0667</v>
+        <v>-0.3518</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6669</v>
+        <v>-1.7558</v>
       </c>
       <c r="G9" t="n">
         <v>-0.804</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4173</v>
+        <v>-0.0901</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.2867</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2878</v>
+        <v>-0.3767</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4189</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5199</v>
+        <v>-3.9551</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2133</v>
+        <v>-3.2225</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3065</v>
+        <v>-0.7326</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8555</v>
+        <v>-3.4496</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6845</v>
+        <v>0.0582</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1709</v>
+        <v>-3.5078</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0668</v>
+        <v>-3.4978</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3825</v>
+        <v>0.0813</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6843</v>
+        <v>-3.5791</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7887</v>
+        <v>0.0482</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.302</v>
+        <v>-0.0231</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4866</v>
+        <v>0.0713</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2804</v>
+        <v>-0.524</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9145</v>
+        <v>-0.314</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.366</v>
+        <v>-0.21</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1786</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5307</v>
+        <v>-4.2497</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3711</v>
+        <v>-2.7949</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1597</v>
+        <v>-1.4547</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3669</v>
+        <v>-1.8555</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5117</v>
+        <v>-0.6845</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1448</v>
+        <v>-1.1709</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7438</v>
+        <v>-1.0668</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3752</v>
+        <v>-0.3825</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6315</v>
+        <v>-0.6843</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6231</v>
+        <v>-0.7887</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1365</v>
+        <v>-0.302</v>
       </c>
       <c r="O11" t="n">
         <v>-0.4866</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0674</v>
+        <v>-1.0102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3952</v>
+        <v>-0.4961</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6721</v>
+        <v>-0.5142</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0698</v>
+        <v>-1.1786</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0698</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8356</v>
+        <v>-4.2779</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9547</v>
+        <v>-2.2665</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8809</v>
+        <v>-2.0115</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.4496</v>
+        <v>-1.3669</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0582</v>
+        <v>-1.5117</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.5078</v>
+        <v>0.1448</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.4978</v>
+        <v>-0.7438</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0813</v>
+        <v>-1.3752</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.5791</v>
+        <v>0.6315</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0482</v>
+        <v>-0.6231</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0231</v>
+        <v>-0.1365</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0713</v>
+        <v>-0.4866</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4374</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q12" t="n">
+        <v>-1.2321</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.8146</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.2906</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.5239</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.0698</v>
+      </c>
+      <c r="W12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.4374</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-1.4045</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-1.0462</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-0.3582</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-1.4189</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.5893</v>
-      </c>
       <c r="X12" t="n">
-        <v>-2.0082</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="13">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.713599999999999</v>
+        <v>4.042900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6360999999999963</v>
+        <v>0.9655000000000009</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0775</v>
+        <v>3.0778</v>
       </c>
       <c r="G13" t="n">
         <v>5.142300000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>5.839700000000001</v>
+        <v>5.8397</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6974</v>
+        <v>-0.6974000000000009</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2125</v>
+        <v>5.212500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>5.227899999999999</v>
+        <v>5.2279</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01529999999999943</v>
+        <v>-0.01529999999999954</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07020000000000007</v>
+        <v>-0.07020000000000004</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6119999999999998</v>
+        <v>0.6119999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6819999999999998</v>
+        <v>-0.6819999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-1.0268</v>
@@ -1468,13 +1468,13 @@
         <v>11.2938</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5815999999999997</v>
+        <v>0.9107000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5408999999999999</v>
+        <v>0.8703000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04070000000000012</v>
+        <v>0.04059999999999997</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9836000000000003</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2308</v>
+        <v>3.5672</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3788</v>
+        <v>1.9811</v>
       </c>
       <c r="F14" t="n">
-        <v>2.852</v>
+        <v>1.5861</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4466</v>
+        <v>2.216</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9179</v>
+        <v>2.0632</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4713</v>
+        <v>0.1529</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6192</v>
+        <v>1.3916</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8828</v>
+        <v>1.1942</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2636</v>
+        <v>0.1973</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1726</v>
+        <v>0.8245</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0351</v>
+        <v>0.8689</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2077</v>
+        <v>-0.0445</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4778</v>
+        <v>1.1807</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2753</v>
+        <v>0.643</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7531</v>
+        <v>0.5377</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0743</v>
+        <v>-0.2402</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1659</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9615</v>
+        <v>2.9134</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4375</v>
+        <v>0.6926</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5241</v>
+        <v>2.2208</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9953</v>
+        <v>0.4466</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3397</v>
+        <v>0.9179</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3445</v>
+        <v>-0.4713</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5073</v>
+        <v>0.6192</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3889</v>
+        <v>0.8828</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1184</v>
+        <v>-0.2636</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5121</v>
+        <v>-0.1726</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0492</v>
+        <v>0.0351</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4629</v>
+        <v>-0.2077</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4448</v>
+        <v>1.1604</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4147</v>
+        <v>0.0385</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.03</v>
+        <v>1.1219</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3843</v>
+        <v>0.0743</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5503</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1659</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.617</v>
+        <v>2.7941</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4581</v>
+        <v>2.2283</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1589</v>
+        <v>0.5659</v>
       </c>
       <c r="G16" t="n">
-        <v>2.216</v>
+        <v>0.9953</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0632</v>
+        <v>1.3397</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1529</v>
+        <v>-0.3445</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3916</v>
+        <v>1.5073</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1942</v>
+        <v>1.3889</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1973</v>
+        <v>0.1184</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8245</v>
+        <v>-0.5121</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8689</v>
+        <v>-0.0492</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0445</v>
+        <v>-0.4629</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2306</v>
+        <v>-0.6122</v>
       </c>
       <c r="T16" t="n">
-        <v>0.12</v>
+        <v>-0.6239</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1106</v>
+        <v>0.0118</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>1.3843</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>1.5503</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4189</v>
+        <v>-0.1659</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0157</v>
+        <v>2.3041</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1512</v>
+        <v>1.0926</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8645</v>
+        <v>1.2114</v>
       </c>
       <c r="G17" t="n">
         <v>3.956</v>
@@ -1780,13 +1780,13 @@
         <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.105</v>
+        <v>-0.8166</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1044</v>
+        <v>-0.1629</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0006</v>
+        <v>-0.6536</v>
       </c>
       <c r="V17" t="n">
         <v>1.0127</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2513</v>
+        <v>0.3106</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0387</v>
       </c>
       <c r="F18" t="n">
-        <v>0.29</v>
+        <v>0.3493</v>
       </c>
       <c r="G18" t="n">
         <v>0.5222</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2976</v>
+        <v>-0.2383</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0581</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2394</v>
+        <v>-0.1801</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5893</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3884</v>
+        <v>-1.0436</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1961</v>
+        <v>-0.8613</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5844</v>
+        <v>-0.1823</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8779</v>
+        <v>-2.8066</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1483</v>
+        <v>-2.8805</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0262</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0163</v>
+        <v>-1.6554</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6152</v>
+        <v>-1.7738</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6315</v>
+        <v>0.1184</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8616</v>
+        <v>-1.1512</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.467</v>
+        <v>-1.1068</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6054</v>
+        <v>-0.0445</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9556</v>
+        <v>1.0238</v>
       </c>
       <c r="T19" t="n">
-        <v>1.348</v>
+        <v>0.3136</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3923</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8768</v>
+        <v>-0.6982</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1088</v>
+        <v>0.4805</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7679</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6764</v>
+        <v>-2.3315</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3843</v>
+        <v>-0.9545</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2921</v>
+        <v>-1.377</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8066</v>
+        <v>-0.8779</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.8805</v>
+        <v>1.1483</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07389999999999999</v>
+        <v>-2.0262</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6554</v>
+        <v>-0.0163</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7738</v>
+        <v>2.6152</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1184</v>
+        <v>-2.6315</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1512</v>
+        <v>-0.8616</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1068</v>
+        <v>-1.467</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0445</v>
+        <v>0.6054</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3909</v>
+        <v>0.0125</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2094</v>
+        <v>0.1973</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6002999999999999</v>
+        <v>-0.1848</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6982</v>
+        <v>-1.8768</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4805</v>
+        <v>-0.1088</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0965</v>
+        <v>-2.788</v>
       </c>
       <c r="E21" t="n">
         <v>-2.142</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9546</v>
+        <v>-0.646</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7176</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9334</v>
+        <v>-0.6248</v>
       </c>
       <c r="T21" t="n">
         <v>-0.283</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6504</v>
+        <v>-0.3418</v>
       </c>
       <c r="V21" t="n">
         <v>0.3491</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7351</v>
+        <v>-3.8066</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5462</v>
+        <v>-3.9646</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1889</v>
+        <v>0.158</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0023</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>0.39</v>
+        <v>0.3186</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6197</v>
+        <v>0.2013</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2297</v>
+        <v>0.1173</v>
       </c>
       <c r="V22" t="n">
         <v>0.3146</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8935</v>
+        <v>-4.2387</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5881</v>
+        <v>-1.1111</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3054</v>
+        <v>-3.1276</v>
       </c>
       <c r="G23" t="n">
         <v>-3.874</v>
@@ -2248,13 +2248,13 @@
         <v>0.2053</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2458</v>
+        <v>-0.5909</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2167</v>
+        <v>-0.3063</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4625</v>
+        <v>-0.2846</v>
       </c>
       <c r="V23" t="n">
         <v>1.253</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.713600000000001</v>
+        <v>-2.319</v>
       </c>
       <c r="E24" t="n">
         <v>-3.077599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6359000000000004</v>
+        <v>0.7585999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-5.142299999999999</v>
@@ -2299,13 +2299,13 @@
         <v>0.6973000000000003</v>
       </c>
       <c r="J24" t="n">
-        <v>0.07020000000000026</v>
+        <v>0.07019999999999937</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6121000000000001</v>
+        <v>-0.6120999999999996</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6822</v>
+        <v>0.6821999999999996</v>
       </c>
       <c r="M24" t="n">
         <v>-5.2126</v>
@@ -2326,13 +2326,13 @@
         <v>12.3206</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5817000000000001</v>
+        <v>0.8132000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.04049999999999976</v>
+        <v>-0.04049999999999992</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5408999999999998</v>
+        <v>0.8539999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>0.9835</v>
@@ -2341,7 +2341,7 @@
         <v>8.1867</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.203</v>
+        <v>-7.202999999999999</v>
       </c>
     </row>
   </sheetData>
